--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486288_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486288_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7382</v>
+        <v>4.2768</v>
       </c>
       <c r="E2" t="n">
-        <v>1.75</v>
+        <v>2.042</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9883</v>
+        <v>2.2348</v>
       </c>
       <c r="G2" t="n">
         <v>0.3947</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5891</v>
+        <v>-0.0505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8304</v>
+        <v>-0.5383</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2413</v>
+        <v>0.4879</v>
       </c>
       <c r="V2" t="n">
         <v>4.1501</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.934</v>
+        <v>3.2067</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1045</v>
+        <v>1.2847</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8295</v>
+        <v>1.922</v>
       </c>
       <c r="G3" t="n">
         <v>0.8673999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4983</v>
+        <v>-0.2256</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8304</v>
+        <v>-0.6501</v>
       </c>
       <c r="U3" t="n">
-        <v>0.332</v>
+        <v>0.4245</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4571</v>
+        <v>2.194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1647</v>
+        <v>0.6122</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2924</v>
+        <v>1.5817</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9558</v>
+        <v>1.0307</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2857</v>
+        <v>-1.5663</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6702</v>
+        <v>2.597</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3986</v>
+        <v>1.2539</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2317</v>
+        <v>-1.5964</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6303</v>
+        <v>2.8504</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5572</v>
+        <v>-0.2233</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5173</v>
+        <v>0.0302</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0399</v>
+        <v>-0.2534</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6527</v>
+        <v>0.0535</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3257</v>
+        <v>-0.6417</v>
       </c>
       <c r="U4" t="n">
-        <v>1.327</v>
+        <v>0.6952</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9384</v>
+        <v>1.4428</v>
       </c>
       <c r="E5" t="n">
-        <v>0.295</v>
+        <v>-0.3256</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6434</v>
+        <v>1.7684</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0307</v>
+        <v>-0.9558</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5663</v>
+        <v>-0.2857</v>
       </c>
       <c r="I5" t="n">
-        <v>2.597</v>
+        <v>-0.6702</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2539</v>
+        <v>-0.3986</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5964</v>
+        <v>0.2317</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8504</v>
+        <v>-0.6303</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2233</v>
+        <v>-0.5572</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0302</v>
+        <v>-0.5173</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2534</v>
+        <v>-0.0399</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2021</v>
+        <v>0.6384</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9589</v>
+        <v>-0.1646</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7568</v>
+        <v>0.803</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1889</v>
+        <v>0.8862</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7195</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5306</v>
+        <v>0.8089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5528999999999999</v>
+        <v>-0.3353</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7298</v>
+        <v>0.1093</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1769</v>
+        <v>-0.4447</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1746</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0981</v>
+        <v>0.3102</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>0.1912</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6217</v>
+        <v>-0.8368</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3683</v>
+        <v>-0.2009</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2534</v>
+        <v>-0.6359</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.853</v>
+        <v>0.569</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3942</v>
+        <v>-0.2067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4588</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3045</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1507</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1588</v>
+        <v>0.7071</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8175</v>
+        <v>-1.0843</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9763</v>
+        <v>1.7914</v>
       </c>
       <c r="G7" t="n">
         <v>0.0936</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8477</v>
+        <v>0.396</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1286</v>
+        <v>-0.1382</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7191</v>
+        <v>0.5341</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0776</v>
+        <v>0.6802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2071</v>
+        <v>2.2724</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8706</v>
+        <v>-1.5922</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3353</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1093</v>
+        <v>0.7298</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4447</v>
+        <v>-0.1769</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5014999999999999</v>
+        <v>1.1746</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3102</v>
+        <v>1.0981</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1912</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8368</v>
+        <v>-0.6217</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2009</v>
+        <v>-0.3683</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6359</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7604</v>
+        <v>0.3443</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0769</v>
+        <v>-0.0529</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8373</v>
+        <v>0.3972</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.3045</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0955</v>
+        <v>0.4191</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2649</v>
+        <v>0.0956</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1694</v>
+        <v>0.3235</v>
       </c>
       <c r="G9" t="n">
         <v>1.4167</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2518</v>
+        <v>0.2629</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.548</v>
+        <v>-0.1875</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2962</v>
+        <v>0.4503</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3904</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5714</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7731</v>
+        <v>-0.3261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2017</v>
+        <v>0.2634</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6245000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3819</v>
+        <v>0.1268</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2346</v>
+        <v>0.2962</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9807</v>
+        <v>-0.7388</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4015</v>
+        <v>-1.2212</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4208</v>
+        <v>0.4824</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5031</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5429</v>
+        <v>-0.301</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>-0.3677</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005</v>
+        <v>0.0667</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4706</v>
+        <v>-0.9752</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5671</v>
+        <v>-1.3183</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0965</v>
+        <v>0.3431</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1555</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5326</v>
+        <v>-0.0373</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.548</v>
+        <v>-0.2992</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0154</v>
+        <v>0.262</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8842</v>
+        <v>-2.5181</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7074</v>
+        <v>-3.3721</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8232</v>
+        <v>0.854</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7741</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.37</v>
+        <v>-0.0039</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.548</v>
+        <v>-0.2127</v>
       </c>
       <c r="U13" t="n">
-        <v>0.178</v>
+        <v>0.2088</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.490600000000001</v>
+        <v>9.5181</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.290700000000001</v>
+        <v>-1.263400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7815</v>
+        <v>10.7814</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9923000000000006</v>
@@ -1546,13 +1546,13 @@
         <v>11.9627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7451</v>
+        <v>1.7726</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6566</v>
+        <v>-3.629</v>
       </c>
       <c r="U14" t="n">
-        <v>5.4015</v>
+        <v>5.4016</v>
       </c>
       <c r="V14" t="n">
         <v>5.4754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.203</v>
+        <v>3.6866</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8331</v>
+        <v>3.1625</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3699</v>
+        <v>0.5241</v>
       </c>
       <c r="G15" t="n">
         <v>3.8386</v>
@@ -1624,13 +1624,13 @@
         <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7793</v>
+        <v>0.2629</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7367</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0427</v>
+        <v>0.1968</v>
       </c>
       <c r="V15" t="n">
         <v>1.3252</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2301</v>
+        <v>3.4729</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5053</v>
+        <v>1.8406</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7248</v>
+        <v>1.6323</v>
       </c>
       <c r="G16" t="n">
         <v>2.343</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2227</v>
+        <v>0.0201</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0959</v>
+        <v>-0.7607</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8733</v>
+        <v>0.7808</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9647</v>
+        <v>0.5986</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5316</v>
+        <v>0.1964</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4331</v>
+        <v>0.4023</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8898</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2895</v>
+        <v>-0.0766</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2824</v>
+        <v>-0.6177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5719</v>
+        <v>0.5411</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.541</v>
+        <v>0.4756</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1484</v>
+        <v>0.1869</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6894</v>
+        <v>0.2886</v>
       </c>
       <c r="G18" t="n">
         <v>-0.08699999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0837</v>
+        <v>0.0183</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0427</v>
+        <v>0.642</v>
       </c>
       <c r="V18" t="n">
         <v>0.5443</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1113</v>
+        <v>-0.4628</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1289</v>
+        <v>-2.2406</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2402</v>
+        <v>1.7779</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2484</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.1331</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5564</v>
+        <v>-0.6681</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2636</v>
+        <v>0.8012</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2959</v>
+        <v>-0.6639</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1133</v>
+        <v>-1.6662</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8174</v>
+        <v>1.0023</v>
       </c>
       <c r="G20" t="n">
         <v>0.901</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8717</v>
+        <v>-0.2397</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4384</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5667</v>
+        <v>0.7516</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3252</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4741</v>
+        <v>-1.4856</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4351</v>
+        <v>-0.3233</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.039</v>
+        <v>-1.1623</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0259</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2312</v>
+        <v>-0.2427</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5907</v>
+        <v>0.4675</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7563</v>
+        <v>-1.5521</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8401</v>
+        <v>-1.7283</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0837</v>
+        <v>0.1762</v>
       </c>
       <c r="G22" t="n">
         <v>-2.128</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4983</v>
+        <v>-0.2941</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0189</v>
+        <v>0.0736</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6495</v>
+        <v>-2.6804</v>
       </c>
       <c r="E23" t="n">
         <v>-3.5698</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9202</v>
+        <v>0.8894</v>
       </c>
       <c r="G23" t="n">
         <v>1.4896</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0359</v>
+        <v>0.0051</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4194</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4553</v>
+        <v>0.4245</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9621</v>
+        <v>-4.4626</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1446</v>
+        <v>-3.8244</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8174</v>
+        <v>-0.6382</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8256</v>
+        <v>-1.3751</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4231</v>
+        <v>-1.399</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4024</v>
+        <v>0.0239</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0678</v>
+        <v>-1.0004</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0678</v>
+        <v>-1.2132</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.2128</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2422</v>
+        <v>-0.3747</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6446</v>
+        <v>-0.1858</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4024</v>
+        <v>-0.1889</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7759</v>
+        <v>-0.6525</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0106</v>
+        <v>-0.6489</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2347</v>
+        <v>-0.0036</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8249</v>
+        <v>-1.13</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8249</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4028</v>
+        <v>-5.4169</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2714</v>
+        <v>-2.8152</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1314</v>
+        <v>-2.6017</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.3751</v>
+        <v>-1.8256</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.399</v>
+        <v>-1.4231</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0239</v>
+        <v>-0.4024</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0004</v>
+        <v>-2.0678</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2132</v>
+        <v>-2.0678</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2128</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3747</v>
+        <v>0.2422</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1858</v>
+        <v>0.6446</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1889</v>
+        <v>-0.4024</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R25" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5927</v>
+        <v>0.3212</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0959</v>
+        <v>0.3401</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4968</v>
+        <v>-0.0189</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.13</v>
+        <v>-2.8249</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.13</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.490600000000001</v>
+        <v>-8.490600000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.7816</v>
+        <v>-10.7814</v>
       </c>
       <c r="F26" t="n">
-        <v>2.290900000000001</v>
+        <v>2.2909</v>
       </c>
       <c r="G26" t="n">
         <v>0.9923999999999997</v>
@@ -2473,7 +2473,7 @@
         <v>-3.3789</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.262700000000001</v>
+        <v>-3.2627</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.9628</v>
@@ -2482,16 +2482,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7451</v>
+        <v>-0.7449000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.401499999999999</v>
+        <v>-5.401600000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>4.656499999999999</v>
+        <v>4.6566</v>
       </c>
       <c r="V26" t="n">
-        <v>-5.4753</v>
+        <v>-5.475300000000001</v>
       </c>
       <c r="W26" t="n">
         <v>4.1708</v>
